--- a/media/file/B0FNCSTQY1/B0FNCSTQY1_ROI-US-pack.xlsx
+++ b/media/file/B0FNCSTQY1/B0FNCSTQY1_ROI-US-pack.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>184.96</t>
+          <t>-61.58</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>1272.54</t>
+          <t>-418.10</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>5548.86</t>
+          <t>-1847.29</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>38176.14</t>
+          <t>-12543.11</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>18.36</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>47.43</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>29.46</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>1827.69</t>
+          <t>779.72</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>628.96</t>
+          <t>-165.02</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>80.29</t>
+          <t>-26.38</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>12.77</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
